--- a/base_prov_co/cruz_verde/cruz_verde_abbott_2026_09_17.xlsx
+++ b/base_prov_co/cruz_verde/cruz_verde_abbott_2026_09_17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O50"/>
+  <dimension ref="A1:P50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,55 +451,60 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>MARCA</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>categoria</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>seller</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>ventas</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>valoracion</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>reviews</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>img_count</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>video_count</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>title_count_characters</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>count_character_desc</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>url_producto</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>disponibilidad</t>
         </is>
@@ -526,15 +531,14 @@
           <t>8427030008608</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>ENSURE</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -547,22 +551,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
         <v>5</v>
       </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
       <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
         <v>53</v>
       </c>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>https://www.cruzverde.com.co/ensure-advance-vainilla-con-proteina--hmb-polvo-850g/COCV_129816.html</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -589,15 +597,14 @@
           <t>7703186032157</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>ENSURE</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -610,22 +617,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
         <v>1</v>
       </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
       <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
         <v>46</v>
       </c>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>https://www.cruzverde.com.co/promo-ensure-advance-lata-x-850g--lata-x-400g/COCV_163576.html</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -652,15 +663,14 @@
           <t>8710428018670</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>ENSURE</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -673,22 +683,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
         <v>5</v>
       </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>57</v>
       </c>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>https://www.cruzverde.com.co/ensure-advance-vainilla-liquido-220-ml/COCV_402006.html</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -715,15 +729,14 @@
           <t>7703186033031</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>ENSURE</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -736,22 +749,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
         <v>1</v>
       </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
       <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
         <v>71</v>
       </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>https://www.cruzverde.com.co/ensure-advance-vainilla-con-proteina-liquido-220-ml-caja-por-6-unidades/COCV_547197.html</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -778,15 +795,14 @@
           <t>8427030008592</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>ENSURE</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -799,22 +815,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
         <v>5</v>
       </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
       <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
         <v>53</v>
       </c>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>https://www.cruzverde.com.co/ensure-advance-vainilla-con-proteina--hmb-polvo-400g/COCV_111380.html</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -841,15 +861,14 @@
           <t>8710428018717</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>ENSURE</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -862,22 +881,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
         <v>5</v>
       </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
       <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
         <v>57</v>
       </c>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>https://www.cruzverde.com.co/ensure-advance-fresa-con-proteina--hmb-liquido-220-ml/COCV_402008.html</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -904,15 +927,14 @@
           <t>8710428013859</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>ENSURE</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -925,22 +947,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
         <v>5</v>
       </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
       <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
         <v>50</v>
       </c>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>https://www.cruzverde.com.co/ensure-advance-fresa-con-proteina--hmb-polvo-850g/COCV_163112.html</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -967,15 +993,14 @@
           <t>8710428013873</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>ENSURE</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -988,22 +1013,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
         <v>3</v>
       </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
       <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
         <v>50</v>
       </c>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>https://www.cruzverde.com.co/ensure-advance-fresa-polvo-400-gr/COCV_163111.html</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -1030,15 +1059,14 @@
           <t>8710428018694</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>ENSURE</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1051,22 +1079,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J10" t="n">
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
         <v>5</v>
       </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
       <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
         <v>58</v>
       </c>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>https://www.cruzverde.com.co/ensure-advance-chocolate-con-proteina--hmb-liquido-220-ml/COCV_402007.html</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -1093,15 +1125,14 @@
           <t>8427030003153</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>ENSURE</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1114,22 +1145,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J11" t="n">
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
         <v>5</v>
       </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
       <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
         <v>31</v>
       </c>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>https://www.cruzverde.com.co/ensure-base-vainilla-polvo-400g/COCV_109254.html</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -1156,15 +1191,14 @@
           <t>8710428019561</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>ENSURE</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1177,22 +1211,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J12" t="n">
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
         <v>5</v>
       </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
       <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
         <v>35</v>
       </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>https://www.cruzverde.com.co/ensure-vainilla-liquido-220-ml/COCV_532007.html</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -1219,15 +1257,14 @@
           <t>8710428018861</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>ENSURE</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1240,22 +1277,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J13" t="n">
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
         <v>5</v>
       </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
       <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
         <v>53</v>
       </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>https://www.cruzverde.com.co/ensure-advance-cafe-liquido-220-ml/COCV_530022.html</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -1282,15 +1323,14 @@
           <t>7703186341334</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>ENSURE</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1303,22 +1343,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J14" t="n">
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
         <v>5</v>
       </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
       <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
         <v>49</v>
       </c>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>https://www.cruzverde.com.co/ensure-advance-nutricion-especializada-tarro-400gr-cafe/COCV_578454.html</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -1345,15 +1389,14 @@
           <t>8427030008943</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>GLUCERNA</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1366,22 +1409,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J15" t="n">
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
         <v>5</v>
       </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
       <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
         <v>50</v>
       </c>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>https://www.cruzverde.com.co/glucerna-tarro-x-850gr-vainilla/COCV_577824.html</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="P15" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -1408,15 +1455,14 @@
           <t>7703186030283</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>GLUCERNA</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1429,22 +1475,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J16" t="n">
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
         <v>5</v>
       </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
       <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
         <v>54</v>
       </c>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>https://www.cruzverde.com.co/glucerna-vainilla-liquido-220-ml/COCV_128687.html</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -1471,15 +1521,14 @@
           <t>7703186499844</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>GLUCERNA</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1492,22 +1541,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J17" t="n">
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
         <v>1</v>
       </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
       <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
         <v>82</v>
       </c>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>https://www.cruzverde.com.co/promo-glucerna-descuento-paquete-por-1-tarro-por-850gr-1-tarro-por-400gr-vainilla/COCV_572641.html</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="P17" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -1534,15 +1587,14 @@
           <t>7703186032737</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>GLUCERNA</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1555,22 +1607,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J18" t="n">
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
         <v>1</v>
       </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
       <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
         <v>52</v>
       </c>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>https://www.cruzverde.com.co/glucerna-vainilla-liquido-220-ml-caja-x6-unidades/COCV_547912.html</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -1597,15 +1653,14 @@
           <t>7703186031525</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>GLUCERNA</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1618,22 +1673,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J19" t="n">
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
         <v>3</v>
       </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
       <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
         <v>51</v>
       </c>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>https://www.cruzverde.com.co/glucerna-fresa-liquido-220-ml/COCV_138288.html</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
+      <c r="P19" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -1660,15 +1719,14 @@
           <t>8427030008936</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>GLUCERNA</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1681,22 +1739,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J20" t="n">
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
         <v>5</v>
       </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
       <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
         <v>50</v>
       </c>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t>https://www.cruzverde.com.co/glucerna-vainilla-polvo-400-gr/COCV_142214.html</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
+      <c r="P20" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -1723,15 +1785,14 @@
           <t>8427030009346</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>GLUCERNA</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1744,22 +1805,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J21" t="n">
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
         <v>1</v>
       </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
       <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
         <v>24</v>
       </c>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>https://www.larebajavirtual.com/glucerna-capuchino-polvo-157457/p</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
+      <c r="P21" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -1786,15 +1851,14 @@
           <t>7501033957376</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>PEDIALYTE</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1807,22 +1871,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J22" t="n">
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
         <v>1</v>
       </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
       <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
         <v>46</v>
       </c>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t>https://www.cruzverde.com.co/suero-de-rehidratacion-pedialyte-max-60-uva-500-ml/COCV_96738.html</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
+      <c r="P22" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -1849,15 +1917,14 @@
           <t>7501033961557</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>PEDIALYTE</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1870,22 +1937,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J23" t="n">
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
         <v>1</v>
       </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
       <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
         <v>61</v>
       </c>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr">
+      <c r="O23" t="inlineStr">
         <is>
           <t>https://www.cruzverde.com.co/suero-de-rehidratacion-pedialyte-max-60-fresa-500-ml/COCV_165575.html</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
+      <c r="P23" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -1912,15 +1983,14 @@
           <t>7501033957369</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>PEDIALYTE</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1933,22 +2003,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J24" t="n">
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
         <v>1</v>
       </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
       <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
         <v>57</v>
       </c>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr">
+      <c r="O24" t="inlineStr">
         <is>
           <t>https://www.cruzverde.com.co/suero-de-rehidratacion-pedialyte-max-60-manzana-500-ml/COCV_96736.html</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
+      <c r="P24" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -1975,15 +2049,14 @@
           <t>7501033961540</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>PEDIALYTE</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1996,22 +2069,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J25" t="n">
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
         <v>1</v>
       </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
       <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
         <v>47</v>
       </c>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr">
+      <c r="O25" t="inlineStr">
         <is>
           <t>https://www.cruzverde.com.co/suero-de-rehidratacion-pedialyte-max-60-coco-500-ml/COCV_165574.html</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr">
+      <c r="P25" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -2038,15 +2115,14 @@
           <t>7501033959967</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>PEDIALYTE</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2059,22 +2135,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J26" t="n">
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
         <v>1</v>
       </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
       <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
         <v>52</v>
       </c>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr">
+      <c r="O26" t="inlineStr">
         <is>
           <t>https://www.cruzverde.com.co/suero-de-rehidratacion-pedialyte-active-30-cereza-500-ml/COCV_134768.html</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
+      <c r="P26" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -2101,15 +2181,14 @@
           <t>7501033957413</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>PEDIALYTE</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2122,22 +2201,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J27" t="n">
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
         <v>1</v>
       </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
       <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
         <v>51</v>
       </c>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr">
+      <c r="O27" t="inlineStr">
         <is>
           <t>https://www.cruzverde.com.co/suero-de-rehidratacion-pedialyte-active-45-fresa-500-ml/COCV_96734.html</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr">
+      <c r="P27" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -2164,15 +2247,14 @@
           <t>7501033959974</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>PEDIALYTE</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2185,22 +2267,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J28" t="n">
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
         <v>1</v>
       </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
       <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
         <v>50</v>
       </c>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr">
+      <c r="O28" t="inlineStr">
         <is>
           <t>https://www.cruzverde.com.co/suero-de-rehidratacion-pedialyte-active-30-coco-500-ml/COCV_134770.html</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr">
+      <c r="P28" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -2227,15 +2313,14 @@
           <t>7501033959950</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>PEDIALYTE</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2248,22 +2333,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J29" t="n">
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
         <v>1</v>
       </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
       <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
         <v>53</v>
       </c>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr">
+      <c r="O29" t="inlineStr">
         <is>
           <t>https://www.cruzverde.com.co/suero-de-rehidratacion-pedialyte-active-30-manzana-500-ml/COCV_134769.html</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr">
+      <c r="P29" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -2290,15 +2379,14 @@
           <t>7501033959981</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>PEDIALYTE</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2311,22 +2399,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J30" t="n">
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
         <v>1</v>
       </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
       <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
         <v>53</v>
       </c>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr">
+      <c r="O30" t="inlineStr">
         <is>
           <t>https://www.cruzverde.com.co/suero-de-rehidratacion-pedialyte-active-30-durazno-500-ml/COCV_134771.html</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr">
+      <c r="P30" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -2353,15 +2445,14 @@
           <t>7501033962394</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>PEDIALYTE</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2374,22 +2465,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J31" t="n">
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
         <v>1</v>
       </c>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
       <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
         <v>53</v>
       </c>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr">
+      <c r="O31" t="inlineStr">
         <is>
           <t>https://www.cruzverde.com.co/suero-de-rehidratacion-pedialyte-active-45-guarana-500-ml/COCV_394640.html</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr">
+      <c r="P31" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -2416,15 +2511,14 @@
           <t>8886451012074</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>PEDIASURE</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2437,22 +2531,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J32" t="n">
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K32" t="n">
         <v>4</v>
       </c>
-      <c r="K32" t="n">
-        <v>0</v>
-      </c>
       <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
         <v>52</v>
       </c>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr">
+      <c r="O32" t="inlineStr">
         <is>
           <t>https://www.cruzverde.com.co/pediasure-peptigro-tarro-por-400gr-fresa/COCV_574284.html</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr">
+      <c r="P32" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -2479,15 +2577,14 @@
           <t>8886451007049</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>PEDIASURE</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2500,22 +2597,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J33" t="n">
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K33" t="n">
         <v>5</v>
       </c>
-      <c r="K33" t="n">
-        <v>0</v>
-      </c>
       <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
         <v>56</v>
       </c>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr">
+      <c r="O33" t="inlineStr">
         <is>
           <t>https://www.cruzverde.com.co/pediasure-10kcalml-lata-x-1600gr-vainilla/COCV_556914.html</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr">
+      <c r="P33" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -2542,15 +2643,14 @@
           <t>8886451012043</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>PEDIASURE</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2563,22 +2663,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J34" t="n">
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K34" t="n">
         <v>5</v>
       </c>
-      <c r="K34" t="n">
-        <v>0</v>
-      </c>
       <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
         <v>55</v>
       </c>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr">
+      <c r="O34" t="inlineStr">
         <is>
           <t>https://www.cruzverde.com.co/pediasure-peptigro-tarro-por-400gr-vainilla/COCV_574305.html</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr">
+      <c r="P34" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -2605,15 +2709,14 @@
           <t>8710428020185</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>PEDIASURE</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2626,22 +2729,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J35" t="n">
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K35" t="n">
         <v>5</v>
       </c>
-      <c r="K35" t="n">
-        <v>0</v>
-      </c>
       <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
         <v>59</v>
       </c>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr">
+      <c r="O35" t="inlineStr">
         <is>
           <t>https://www.cruzverde.com.co/pediasure-vainilla-liquido-220ml/COCV_525504.html</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr">
+      <c r="P35" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -2668,15 +2775,14 @@
           <t>8710428020314</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>PEDIASURE</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2689,22 +2795,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J36" t="n">
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K36" t="n">
         <v>5</v>
       </c>
-      <c r="K36" t="n">
-        <v>0</v>
-      </c>
       <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
         <v>56</v>
       </c>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr">
+      <c r="O36" t="inlineStr">
         <is>
           <t>https://www.cruzverde.com.co/pediasure-fresa-liquido-220-ml/COCV_525503.html</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr">
+      <c r="P36" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -2731,15 +2841,14 @@
           <t>8886451012036</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>PEDIASURE</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2752,22 +2861,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J37" t="n">
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K37" t="n">
         <v>5</v>
       </c>
-      <c r="K37" t="n">
-        <v>0</v>
-      </c>
       <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
         <v>52</v>
       </c>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr">
+      <c r="O37" t="inlineStr">
         <is>
           <t>https://www.cruzverde.com.co/pediasure-peptigro-tarro-por-850gr-fresa/COCV_574283.html</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr">
+      <c r="P37" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -2794,15 +2907,14 @@
           <t>8886451012029</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>PEDIASURE</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2815,22 +2927,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J38" t="n">
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K38" t="n">
         <v>4</v>
       </c>
-      <c r="K38" t="n">
-        <v>0</v>
-      </c>
       <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
         <v>52</v>
       </c>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr">
+      <c r="O38" t="inlineStr">
         <is>
           <t>https://www.cruzverde.com.co/pediasure-peptigro-tarro-por-400gr-fresa/COCV_574284.html</t>
         </is>
       </c>
-      <c r="O38" t="inlineStr">
+      <c r="P38" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -2857,15 +2973,14 @@
           <t>7703186033130</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>PEDIASURE</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2878,22 +2993,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J39" t="n">
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K39" t="n">
         <v>1</v>
       </c>
-      <c r="K39" t="n">
-        <v>0</v>
-      </c>
       <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
         <v>65</v>
       </c>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr">
+      <c r="O39" t="inlineStr">
         <is>
           <t>https://www.cruzverde.com.co/promo-pediasure-abbott-precio-especial-10-kcal-ml-caja-x-6bot-x-220ml-vainilla/COCV_547911.html</t>
         </is>
       </c>
-      <c r="O39" t="inlineStr">
+      <c r="P39" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -2920,15 +3039,14 @@
           <t>8710428024039</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>PEDIASURE</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2941,22 +3059,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J40" t="n">
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K40" t="n">
         <v>4</v>
       </c>
-      <c r="K40" t="n">
-        <v>0</v>
-      </c>
       <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
         <v>71</v>
       </c>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr">
+      <c r="O40" t="inlineStr">
         <is>
           <t>https://www.cruzverde.com.co/pediasure-nutricion-especializada-10-anos-frasco-220ml-vainilla/COCV_578455.html</t>
         </is>
       </c>
-      <c r="O40" t="inlineStr">
+      <c r="P40" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -2983,15 +3105,14 @@
           <t>7703186863072</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3004,22 +3125,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J41" t="n">
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K41" t="n">
         <v>3</v>
       </c>
-      <c r="K41" t="n">
-        <v>0</v>
-      </c>
       <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
         <v>33</v>
       </c>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr">
+      <c r="O41" t="inlineStr">
         <is>
           <t>https://www.cruzverde.com.co/formula-infantil-similac-1-hmo-polvo-1400-gr/COCV_547206.html</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr">
+      <c r="P41" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -3046,15 +3171,14 @@
           <t>5099864017014</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3067,22 +3191,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J42" t="n">
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K42" t="n">
         <v>3</v>
       </c>
-      <c r="K42" t="n">
-        <v>0</v>
-      </c>
       <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
         <v>32</v>
       </c>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr">
+      <c r="O42" t="inlineStr">
         <is>
           <t>https://www.cruzverde.com.co/formula-infantil-similac-2-5hmo-polvo-800-gr/COCV_545921.html</t>
         </is>
       </c>
-      <c r="O42" t="inlineStr">
+      <c r="P42" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -3109,15 +3237,14 @@
           <t>5099864017229</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3130,22 +3257,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J43" t="n">
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K43" t="n">
         <v>4</v>
       </c>
-      <c r="K43" t="n">
-        <v>0</v>
-      </c>
       <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="n">
         <v>33</v>
       </c>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr">
+      <c r="O43" t="inlineStr">
         <is>
           <t>https://www.cruzverde.com.co/formula-infantil-similac-3-5hmo-polvo-1800gr/COCV_547215.html</t>
         </is>
       </c>
-      <c r="O43" t="inlineStr">
+      <c r="P43" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -3172,15 +3303,14 @@
           <t>5099864017212</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3193,22 +3323,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J44" t="n">
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K44" t="n">
         <v>3</v>
       </c>
-      <c r="K44" t="n">
-        <v>0</v>
-      </c>
       <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
         <v>32</v>
       </c>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr">
+      <c r="O44" t="inlineStr">
         <is>
           <t>https://www.cruzverde.com.co/similac-3-5-hmos-kid-lata-x-800gr-vainilla/COCV_547208.html</t>
         </is>
       </c>
-      <c r="O44" t="inlineStr">
+      <c r="P44" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -3235,15 +3369,14 @@
           <t>5099864017205</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3256,22 +3389,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J45" t="n">
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K45" t="n">
         <v>3</v>
       </c>
-      <c r="K45" t="n">
-        <v>0</v>
-      </c>
       <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
         <v>32</v>
       </c>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr">
+      <c r="O45" t="inlineStr">
         <is>
           <t>https://www.cruzverde.com.co/similac-3-5-hmos-kid-lata-x-350gr-vainilla/COCV_546988.html</t>
         </is>
       </c>
-      <c r="O45" t="inlineStr">
+      <c r="P45" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -3298,15 +3435,14 @@
           <t>8427030004938</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3319,22 +3455,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J46" t="n">
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K46" t="n">
         <v>3</v>
       </c>
-      <c r="K46" t="n">
-        <v>0</v>
-      </c>
       <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
         <v>45</v>
       </c>
-      <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr">
+      <c r="O46" t="inlineStr">
         <is>
           <t>https://www.cruzverde.com.co/similac-antireflujo-tarro-x-375gr/COCV_113960.html</t>
         </is>
       </c>
-      <c r="O46" t="inlineStr">
+      <c r="P46" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -3361,15 +3501,14 @@
           <t>8427030003658</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3382,22 +3521,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J47" t="n">
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K47" t="n">
         <v>3</v>
       </c>
-      <c r="K47" t="n">
-        <v>0</v>
-      </c>
       <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="n">
         <v>51</v>
       </c>
-      <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr">
+      <c r="O47" t="inlineStr">
         <is>
           <t>https://www.cruzverde.com.co/formula-infantil-similac-neosure-polvo-370-gr/COCV_100466.html</t>
         </is>
       </c>
-      <c r="O47" t="inlineStr">
+      <c r="P47" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -3424,15 +3567,14 @@
           <t>5099864017236</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3445,22 +3587,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J48" t="n">
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K48" t="n">
         <v>3</v>
       </c>
-      <c r="K48" t="n">
-        <v>0</v>
-      </c>
       <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="n">
         <v>55</v>
       </c>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr">
+      <c r="O48" t="inlineStr">
         <is>
           <t>https://www.cruzverde.com.co/similac-arroz-hmo-lactantes-0-12-meses-lata-x-400gr/COCV_544508.html</t>
         </is>
       </c>
-      <c r="O48" t="inlineStr">
+      <c r="P48" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -3487,15 +3633,14 @@
           <t>8427030003238</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3508,22 +3653,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J49" t="n">
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K49" t="n">
         <v>3</v>
       </c>
-      <c r="K49" t="n">
-        <v>0</v>
-      </c>
       <c r="L49" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" t="n">
         <v>54</v>
       </c>
-      <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr">
+      <c r="O49" t="inlineStr">
         <is>
           <t>https://www.cruzverde.com.co/formula-infantil-similac-sin-lactosa-polvo-375-gr/COCV_96845.html</t>
         </is>
       </c>
-      <c r="O49" t="inlineStr">
+      <c r="P49" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -3550,15 +3699,14 @@
           <t>7703186032355</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3571,22 +3719,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J50" t="n">
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K50" t="n">
         <v>3</v>
       </c>
-      <c r="K50" t="n">
-        <v>0</v>
-      </c>
       <c r="L50" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" t="n">
         <v>41</v>
       </c>
-      <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr">
+      <c r="O50" t="inlineStr">
         <is>
           <t>https://www.cruzverde.com.co/formula-infantil-similac-total-comfort-etapa-1-polvo-1400-gr/COCV_146187.html</t>
         </is>
       </c>
-      <c r="O50" t="inlineStr">
+      <c r="P50" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
